--- a/modelos/modelo_npcs.xlsx
+++ b/modelos/modelo_npcs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="217">
   <si>
     <t>Nome</t>
   </si>
@@ -27,9 +27,15 @@
     <t>Dificuldade</t>
   </si>
   <si>
+    <t>Profissão</t>
+  </si>
+  <si>
     <t>Classe</t>
   </si>
   <si>
+    <t>Especialização</t>
+  </si>
+  <si>
     <t>Idade</t>
   </si>
   <si>
@@ -54,63 +60,96 @@
     <t>Dinheiro</t>
   </si>
   <si>
-    <t>Atr: Força</t>
-  </si>
-  <si>
-    <t>Atr: Destreza</t>
-  </si>
-  <si>
-    <t>Atr: Vigor</t>
-  </si>
-  <si>
-    <t>Atr: Inteligência</t>
-  </si>
-  <si>
-    <t>Atr: Percepção</t>
-  </si>
-  <si>
-    <t>Atr: Carisma</t>
-  </si>
-  <si>
-    <t>Atr: Manipulação</t>
+    <t>Atr: FOR</t>
+  </si>
+  <si>
+    <t>Atr: CONS</t>
+  </si>
+  <si>
+    <t>Atr: AGI</t>
+  </si>
+  <si>
+    <t>Atr: DES</t>
+  </si>
+  <si>
+    <t>Atr: INT</t>
+  </si>
+  <si>
+    <t>Atr: PER</t>
+  </si>
+  <si>
+    <t>Atr: CAR</t>
+  </si>
+  <si>
+    <t>Atr: WILL</t>
+  </si>
+  <si>
+    <t>Per: Arma Branca</t>
+  </si>
+  <si>
+    <t>Per: Armas de Fogo</t>
   </si>
   <si>
     <t>Per: Briga</t>
   </si>
   <si>
-    <t>Per: Armas brancas</t>
-  </si>
-  <si>
-    <t>Per: Armas de fogo</t>
-  </si>
-  <si>
-    <t>Per: Furtividade</t>
-  </si>
-  <si>
-    <t>Per: Atletismo</t>
-  </si>
-  <si>
-    <t>Per: Investigação</t>
+    <t>Per: Armadilhas</t>
+  </si>
+  <si>
+    <t>Per: Esportes</t>
+  </si>
+  <si>
+    <t>Per: Condução</t>
+  </si>
+  <si>
+    <t>Per: Extração</t>
+  </si>
+  <si>
+    <t>Per: Sobrevivência</t>
+  </si>
+  <si>
+    <t>Per: Ciência</t>
+  </si>
+  <si>
+    <t>Per: Computação</t>
+  </si>
+  <si>
+    <t>Per: Engenharia</t>
   </si>
   <si>
     <t>Per: Medicina</t>
   </si>
   <si>
-    <t>Per: Prontidão</t>
-  </si>
-  <si>
-    <t>Per: Persuasão</t>
-  </si>
-  <si>
-    <t>Per: Intimidação</t>
-  </si>
-  <si>
-    <t>Per: Lábia</t>
+    <t>Per: Arte</t>
+  </si>
+  <si>
+    <t>Per: Avaliação de Objetos</t>
+  </si>
+  <si>
+    <t>Per: Espionagem</t>
+  </si>
+  <si>
+    <t>Per: Institucional</t>
+  </si>
+  <si>
+    <t>Per: Jogos</t>
+  </si>
+  <si>
+    <t>Per: Manipulação</t>
+  </si>
+  <si>
+    <t>Per: Sentidos</t>
+  </si>
+  <si>
+    <t>Per: Trato de Animais</t>
   </si>
   <si>
     <t>Vantagens (separe por ;)</t>
   </si>
   <si>
+    <t>Defeitos (separe por ;)</t>
+  </si>
+  <si>
     <t>Itens (ids ou nomes, separe por ;)</t>
   </si>
   <si>
@@ -129,130 +168,502 @@
     <t>Piratas</t>
   </si>
   <si>
-    <t>Sem classe</t>
+    <t>Sobrevivente</t>
+  </si>
+  <si>
+    <t>Caçador</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>Absorver Nutrientes</t>
+  </si>
+  <si>
+    <t>Acumulador</t>
+  </si>
+  <si>
+    <t>faca; capa</t>
+  </si>
+  <si>
+    <t>Exemplo — apague esta linha.</t>
+  </si>
+  <si>
+    <t>Como preencher:</t>
+  </si>
+  <si>
+    <t>• Uma linha por NPC. Só a coluna "Nome" é obrigatória.</t>
+  </si>
+  <si>
+    <t>• "Grupo": se o grupo não existir na campanha, ele é criado na importação.</t>
+  </si>
+  <si>
+    <t>• Colunas "Atr:" são atributos (FOR, CONS, AGI, DES, INT, PER, CAR, WILL) e "Per:" são pontos gastos na perícia base — use números.</t>
+  </si>
+  <si>
+    <t>• PV e Sanidade em branco são calculados pelas regras. Subperícias específicas podem ser ajustadas na ficha depois.</t>
+  </si>
+  <si>
+    <t>• Profissão, Classe, Especialização, Vantagens, Defeitos e Itens: use os nomes da aba Listas. Separe listas por ponto e vírgula (;).</t>
+  </si>
+  <si>
+    <t>• Não mude os títulos da primeira linha. Se as regras mudarem, baixe o modelo de novo pelo app.</t>
+  </si>
+  <si>
+    <t>Profissões</t>
+  </si>
+  <si>
+    <t>Classes</t>
+  </si>
+  <si>
+    <t>Especializações</t>
+  </si>
+  <si>
+    <t>Vantagens</t>
+  </si>
+  <si>
+    <t>Defeitos</t>
+  </si>
+  <si>
+    <t>Item (id)</t>
+  </si>
+  <si>
+    <t>Item (nome)</t>
+  </si>
+  <si>
+    <t>O ARMADILHEIRO (TRAPPER) (Caçador)</t>
+  </si>
+  <si>
+    <t>faca</t>
+  </si>
+  <si>
+    <t>Faca</t>
+  </si>
+  <si>
+    <t>Batedor</t>
+  </si>
+  <si>
+    <t>Ciborgue</t>
+  </si>
+  <si>
+    <t>EXTERMINADOR DE BESTAS (SLAYER) (Caçador)</t>
+  </si>
+  <si>
+    <t>Acerto Mortal</t>
+  </si>
+  <si>
+    <t>Alergia à Maré</t>
+  </si>
+  <si>
+    <t>machado</t>
+  </si>
+  <si>
+    <t>Machado de duas mãos</t>
+  </si>
+  <si>
+    <t>Socorrista</t>
+  </si>
+  <si>
+    <t>Encantado</t>
+  </si>
+  <si>
+    <t>O BASTIÃO (JUGGERNAUT) (Caçador)</t>
+  </si>
+  <si>
+    <t>Ambidestria</t>
+  </si>
+  <si>
+    <t>Asma</t>
+  </si>
+  <si>
+    <t>revolver</t>
+  </si>
+  <si>
+    <t>Revólver</t>
+  </si>
+  <si>
+    <t>Protetor</t>
+  </si>
+  <si>
+    <t>Inventor</t>
+  </si>
+  <si>
+    <t>CORAÇÃO DE ENGRENAGEM (Ciborgue)</t>
+  </si>
+  <si>
+    <t>Ambiente Favorito</t>
+  </si>
+  <si>
+    <t>Azarado</t>
+  </si>
+  <si>
+    <t>escudo</t>
+  </si>
+  <si>
+    <t>Escudo de madeira</t>
+  </si>
+  <si>
+    <t>Coletor</t>
+  </si>
+  <si>
+    <t>Mutante</t>
+  </si>
+  <si>
+    <t>TRANSCENDENTE (Ciborgue)</t>
+  </si>
+  <si>
+    <t>Armadilha Mortal</t>
+  </si>
+  <si>
+    <t>Covarde</t>
+  </si>
+  <si>
+    <t>capacete</t>
+  </si>
+  <si>
+    <t>Capacete de couro</t>
+  </si>
+  <si>
+    <t>Zelador</t>
+  </si>
+  <si>
+    <t>Perito</t>
+  </si>
+  <si>
+    <t>ZORD (Ciborgue)</t>
+  </si>
+  <si>
+    <t>Armadilheiro</t>
+  </si>
+  <si>
+    <t>Curioso Imprudente</t>
+  </si>
+  <si>
+    <t>gibao</t>
+  </si>
+  <si>
+    <t>Gibão acolchoado</t>
+  </si>
+  <si>
+    <t>Soldado</t>
+  </si>
+  <si>
+    <t>O DIPLOMATA (Encantado)</t>
+  </si>
+  <si>
+    <t>Assassino</t>
+  </si>
+  <si>
+    <t>Estômago Sensível</t>
+  </si>
+  <si>
+    <t>capa</t>
+  </si>
+  <si>
+    <t>Capa de viagem</t>
+  </si>
+  <si>
+    <t>Sortudo</t>
+  </si>
+  <si>
+    <t>SUSSURRANTE (Encantado)</t>
+  </si>
+  <si>
+    <t>Ataque Certeiro</t>
+  </si>
+  <si>
+    <t>Fobia leve</t>
+  </si>
+  <si>
+    <t>anel</t>
+  </si>
+  <si>
+    <t>Anel de prata</t>
+  </si>
+  <si>
+    <t>Transmorfo</t>
+  </si>
+  <si>
+    <t>GALANTE (Encantado)</t>
+  </si>
+  <si>
+    <t>Ataque Desarmado Treinado</t>
+  </si>
+  <si>
+    <t>Fotofobia</t>
+  </si>
+  <si>
+    <t>armadilha_urso</t>
+  </si>
+  <si>
+    <t>Armadilha de urso</t>
+  </si>
+  <si>
+    <t>Treinador</t>
+  </si>
+  <si>
+    <t>O ARMEIRO (Inventor)</t>
+  </si>
+  <si>
+    <t>Biblioteca Virtual</t>
+  </si>
+  <si>
+    <t>Hipersensibilidade à Dor</t>
+  </si>
+  <si>
+    <t>corda</t>
+  </si>
+  <si>
+    <t>Corda (15 m)</t>
+  </si>
+  <si>
+    <t>CARRIER CRAFTER (Inventor)</t>
+  </si>
+  <si>
+    <t>Bom Senso</t>
+  </si>
+  <si>
+    <t>Inocente</t>
+  </si>
+  <si>
+    <t>mochila</t>
+  </si>
+  <si>
+    <t>Mochila</t>
+  </si>
+  <si>
+    <t>O ENGENHEIRO DAS RUÍNAS (Inventor)</t>
+  </si>
+  <si>
+    <t>Calejado</t>
+  </si>
+  <si>
+    <t>Insônia</t>
+  </si>
+  <si>
+    <t>ADAPTADO (Mutante)</t>
+  </si>
+  <si>
+    <t>Companheiro Animal</t>
+  </si>
+  <si>
+    <t>Mãos fracas</t>
+  </si>
+  <si>
+    <t>ABERRANTE (Mutante)</t>
+  </si>
+  <si>
     <t>Contatos</t>
   </si>
   <si>
-    <t>faca; capa</t>
-  </si>
-  <si>
-    <t>Exemplo — apague esta linha.</t>
-  </si>
-  <si>
-    <t>Como preencher:</t>
-  </si>
-  <si>
-    <t>• Uma linha por NPC. Só a coluna "Nome" é obrigatória.</t>
-  </si>
-  <si>
-    <t>• "Grupo": se o grupo não existir na campanha, ele é criado na importação.</t>
-  </si>
-  <si>
-    <t>• Colunas "Atr:" são atributos e "Per:" são perícias — use números.</t>
-  </si>
-  <si>
-    <t>• Vantagens e Itens: separe por ponto e vírgula (;). Itens podem ser o id ou o nome do catálogo (aba Listas).</t>
-  </si>
-  <si>
-    <t>• Não mude os títulos da primeira linha. Se as regras mudarem, baixe o modelo de novo pelo app.</t>
-  </si>
-  <si>
-    <t>Classes</t>
-  </si>
-  <si>
-    <t>Vantagens</t>
-  </si>
-  <si>
-    <t>Item (id)</t>
-  </si>
-  <si>
-    <t>Item (nome)</t>
-  </si>
-  <si>
-    <t>Sorte</t>
-  </si>
-  <si>
-    <t>faca</t>
-  </si>
-  <si>
-    <t>Faca</t>
-  </si>
-  <si>
-    <t>Exemplo: Ocultista</t>
-  </si>
-  <si>
-    <t>machado</t>
-  </si>
-  <si>
-    <t>Machado de duas mãos</t>
-  </si>
-  <si>
-    <t>Exemplo: Caçador</t>
-  </si>
-  <si>
-    <t>Resistente</t>
-  </si>
-  <si>
-    <t>revolver</t>
-  </si>
-  <si>
-    <t>Revólver</t>
-  </si>
-  <si>
-    <t>Recursos</t>
-  </si>
-  <si>
-    <t>escudo</t>
-  </si>
-  <si>
-    <t>Escudo de madeira</t>
-  </si>
-  <si>
-    <t>capacete</t>
-  </si>
-  <si>
-    <t>Capacete de couro</t>
-  </si>
-  <si>
-    <t>gibao</t>
-  </si>
-  <si>
-    <t>Gibão acolchoado</t>
-  </si>
-  <si>
-    <t>capa</t>
-  </si>
-  <si>
-    <t>Capa de viagem</t>
-  </si>
-  <si>
-    <t>anel</t>
-  </si>
-  <si>
-    <t>Anel de prata</t>
-  </si>
-  <si>
-    <t>armadilha_urso</t>
-  </si>
-  <si>
-    <t>Armadilha de urso</t>
-  </si>
-  <si>
-    <t>corda</t>
-  </si>
-  <si>
-    <t>Corda (15 m)</t>
-  </si>
-  <si>
-    <t>mochila</t>
-  </si>
-  <si>
-    <t>Mochila</t>
+    <t>Metabolismo Acelerado</t>
+  </si>
+  <si>
+    <t>RADIANTE (a Praga) (Mutante)</t>
+  </si>
+  <si>
+    <t>Corpo Flexível</t>
+  </si>
+  <si>
+    <t>Ossos Frágeis</t>
+  </si>
+  <si>
+    <t>SOCORRISTA (Perito)</t>
+  </si>
+  <si>
+    <t>Defesa Aprimorada</t>
+  </si>
+  <si>
+    <t>Paranoia Sobrevivente</t>
+  </si>
+  <si>
+    <t>O ALQUIMISTA (Perito)</t>
+  </si>
+  <si>
+    <t>Defesa Crítica</t>
+  </si>
+  <si>
+    <t>Pavio Curto</t>
+  </si>
+  <si>
+    <t>HACKER (Perito)</t>
+  </si>
+  <si>
+    <t>Escudo Amigo</t>
+  </si>
+  <si>
+    <t>Resistência baixa</t>
+  </si>
+  <si>
+    <t>O ARTISTA (Perito)</t>
+  </si>
+  <si>
+    <t>Especialista em Combate</t>
+  </si>
+  <si>
+    <t>Sincericídio</t>
+  </si>
+  <si>
+    <t>COMANDANTE (Soldado)</t>
+  </si>
+  <si>
+    <t>Especialista Pericial</t>
+  </si>
+  <si>
+    <t>Sono Pesado</t>
+  </si>
+  <si>
+    <t>OPERAÇÕES ESPECIAIS (BLACK OPS) (Soldado)</t>
+  </si>
+  <si>
+    <t>Genes Fortes</t>
+  </si>
+  <si>
+    <t>Vício Enraizado</t>
+  </si>
+  <si>
+    <t>GUERRILHEIRO (Soldado)</t>
+  </si>
+  <si>
+    <t>Gênio Especialista</t>
+  </si>
+  <si>
+    <t>Tique Nervoso</t>
+  </si>
+  <si>
+    <t>FILHOS DA FORTUNA (Sortudo)</t>
+  </si>
+  <si>
+    <t>Glutão</t>
+  </si>
+  <si>
+    <t>Aura de Presa</t>
+  </si>
+  <si>
+    <t>UNIVERSAIS (Sortudo)</t>
+  </si>
+  <si>
+    <t>Herói</t>
+  </si>
+  <si>
+    <t>Caolho / Visão Debilitada</t>
+  </si>
+  <si>
+    <t>ILUMINADOS (Sortudo)</t>
+  </si>
+  <si>
+    <t>Humano de Carga</t>
+  </si>
+  <si>
+    <t>Desastrado</t>
+  </si>
+  <si>
+    <t>LICANTROPO (Hibrido) (Transmorfo)</t>
+  </si>
+  <si>
+    <t>Improvisar Armadilha</t>
+  </si>
+  <si>
+    <t>Doença crônica</t>
+  </si>
+  <si>
+    <t>MAGNO (Transmorfo)</t>
+  </si>
+  <si>
+    <t>Maestria em combate</t>
+  </si>
+  <si>
+    <t>Gremillin</t>
+  </si>
+  <si>
+    <t>O MÍMICO (Transmorfo)</t>
+  </si>
+  <si>
+    <t>Mercador</t>
+  </si>
+  <si>
+    <t>Hemofobia</t>
+  </si>
+  <si>
+    <t>LÍDER ALFA (Treinador)</t>
+  </si>
+  <si>
+    <t>Meticuloso</t>
+  </si>
+  <si>
+    <t>Imuno suprimido</t>
+  </si>
+  <si>
+    <t>IRMÃO DE ALMA (Soulbound) (Treinador)</t>
+  </si>
+  <si>
+    <t>Poliglota</t>
+  </si>
+  <si>
+    <t>Insônia pós traumática</t>
+  </si>
+  <si>
+    <t>ESPÍRITO ANCESTRAL (Treinador)</t>
+  </si>
+  <si>
+    <t>Reflexos Rápidos</t>
+  </si>
+  <si>
+    <t>Manco</t>
+  </si>
+  <si>
+    <t>Resistente às Drogas</t>
+  </si>
+  <si>
+    <t>Mãos trêmulas</t>
+  </si>
+  <si>
+    <t>Saúde de Ferro</t>
+  </si>
+  <si>
+    <t>Mouco / Surdo</t>
+  </si>
+  <si>
+    <t>Sentido Aguçado</t>
+  </si>
+  <si>
+    <t>Pulmões da Maré</t>
+  </si>
+  <si>
+    <t>Silencioso</t>
+  </si>
+  <si>
+    <t>Regeneração Lenta</t>
+  </si>
+  <si>
+    <t>Simpático</t>
+  </si>
+  <si>
+    <t>Sangue Fino</t>
+  </si>
+  <si>
+    <t>Voz Danificada (Rouco/Mudo)</t>
+  </si>
+  <si>
+    <t>Suporte Especializado</t>
+  </si>
+  <si>
+    <t>Vulnerável</t>
+  </si>
+  <si>
+    <t>Talento Natural</t>
+  </si>
+  <si>
+    <t>Tecnomente</t>
+  </si>
+  <si>
+    <t>Viciado em Perigo</t>
+  </si>
+  <si>
+    <t>Vitalidade</t>
+  </si>
+  <si>
+    <t>Vontade de Ferro</t>
   </si>
 </sst>
 </file>
@@ -643,34 +1054,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AW2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="19" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="12" customWidth="1"/>
-    <col min="22" max="23" width="20" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="16" customWidth="1"/>
-    <col min="26" max="26" width="19" customWidth="1"/>
-    <col min="27" max="27" width="15" customWidth="1"/>
-    <col min="28" max="29" width="16" customWidth="1"/>
-    <col min="30" max="30" width="18" customWidth="1"/>
-    <col min="31" max="31" width="12" customWidth="1"/>
-    <col min="32" max="32" width="26" customWidth="1"/>
-    <col min="33" max="33" width="36" customWidth="1"/>
-    <col min="34" max="34" width="17" customWidth="1"/>
-    <col min="35" max="36" width="12" customWidth="1"/>
+    <col min="25" max="25" width="20" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="17" customWidth="1"/>
+    <col min="28" max="30" width="15" customWidth="1"/>
+    <col min="31" max="31" width="20" customWidth="1"/>
+    <col min="32" max="32" width="14" customWidth="1"/>
+    <col min="33" max="34" width="17" customWidth="1"/>
+    <col min="35" max="35" width="15" customWidth="1"/>
+    <col min="36" max="36" width="12" customWidth="1"/>
+    <col min="37" max="37" width="27" customWidth="1"/>
+    <col min="38" max="38" width="17" customWidth="1"/>
+    <col min="39" max="39" width="20" customWidth="1"/>
+    <col min="40" max="40" width="12" customWidth="1"/>
+    <col min="41" max="41" width="18" customWidth="1"/>
+    <col min="42" max="42" width="15" customWidth="1"/>
+    <col min="43" max="43" width="23" customWidth="1"/>
+    <col min="44" max="44" width="26" customWidth="1"/>
+    <col min="45" max="45" width="25" customWidth="1"/>
+    <col min="46" max="46" width="36" customWidth="1"/>
+    <col min="47" max="47" width="17" customWidth="1"/>
+    <col min="48" max="49" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -779,13 +1195,52 @@
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -794,100 +1249,139 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
+        <v>53</v>
+      </c>
+      <c r="J2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" t="s">
+        <v>53</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="M2">
+        <v>30</v>
+      </c>
+      <c r="N2">
+        <v>10</v>
+      </c>
+      <c r="O2">
         <v>50</v>
       </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-      <c r="O2">
-        <v>3</v>
-      </c>
       <c r="P2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>39</v>
+        <v>2</v>
+      </c>
+      <c r="AF2">
+        <v>2</v>
+      </c>
+      <c r="AG2">
+        <v>2</v>
+      </c>
+      <c r="AH2">
+        <v>2</v>
+      </c>
+      <c r="AI2">
+        <v>2</v>
+      </c>
+      <c r="AJ2">
+        <v>2</v>
+      </c>
+      <c r="AK2">
+        <v>2</v>
+      </c>
+      <c r="AL2">
+        <v>2</v>
+      </c>
+      <c r="AM2">
+        <v>2</v>
+      </c>
+      <c r="AN2">
+        <v>2</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AP2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>2</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -906,32 +1400,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -942,180 +1441,1022 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="1" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>53</v>
-      </c>
       <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
         <v>54</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="E8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="E10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>135</v>
+      </c>
+      <c r="E12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" t="s">
+        <v>165</v>
+      </c>
+      <c r="F21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" t="s">
+        <v>171</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" t="s">
+        <v>174</v>
+      </c>
+      <c r="F24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>178</v>
+      </c>
+      <c r="D26" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" t="s">
+        <v>186</v>
+      </c>
+      <c r="F28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D32" t="s">
+        <v>197</v>
+      </c>
+      <c r="E32" t="s">
+        <v>198</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E33" t="s">
+        <v>200</v>
+      </c>
+      <c r="F33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" t="s">
+        <v>205</v>
+      </c>
+      <c r="E36" t="s">
+        <v>206</v>
+      </c>
+      <c r="F36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" t="s">
+        <v>209</v>
+      </c>
+      <c r="F38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" t="s">
+        <v>211</v>
+      </c>
+      <c r="F39" t="s">
+        <v>53</v>
+      </c>
+      <c r="G39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" t="s">
+        <v>212</v>
+      </c>
+      <c r="E40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" t="s">
+        <v>53</v>
+      </c>
+      <c r="G40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" t="s">
+        <v>213</v>
+      </c>
+      <c r="E41" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" t="s">
+        <v>214</v>
+      </c>
+      <c r="E42" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" t="s">
+        <v>215</v>
+      </c>
+      <c r="E43" t="s">
+        <v>53</v>
+      </c>
+      <c r="F43" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" t="s">
+        <v>216</v>
+      </c>
+      <c r="E44" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
